--- a/第十二道题/B/code/output/Result_Q1.xlsx
+++ b/第十二道题/B/code/output/Result_Q1.xlsx
@@ -493,15 +493,11 @@
   <cols>
     <col min="1" max="1" width="11.625" style="1" customWidth="true"/>
     <col min="6" max="6" width="6.625" customWidth="true"/>
-    <col min="7" max="7" width="11.625" customWidth="true"/>
+    <col min="7" max="11" width="11.625" customWidth="true"/>
     <col min="2" max="2" width="3.19921875" style="1" customWidth="true"/>
     <col min="3" max="3" width="6" style="1" customWidth="true"/>
     <col min="4" max="4" width="4.1328125" style="1" customWidth="true"/>
     <col min="5" max="5" width="4.1328125" style="1" customWidth="true"/>
-    <col min="8" max="8" width="3.19921875" customWidth="true"/>
-    <col min="9" max="9" width="6" customWidth="true"/>
-    <col min="10" max="10" width="4.1328125" customWidth="true"/>
-    <col min="11" max="11" width="4.1328125" customWidth="true"/>
   </cols>
   <sheetData>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" ht="20.25" x14ac:dyDescent="0.25">
@@ -580,15 +576,9 @@
       <c r="H4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="4">
-        <v>5300</v>
-      </c>
-      <c r="J4" s="4">
-        <v>130</v>
-      </c>
-      <c r="K4" s="4">
-        <v>405</v>
-      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
@@ -609,18 +599,10 @@
       <c r="G5" s="4">
         <v>1</v>
       </c>
-      <c r="H5" s="4">
-        <v>2</v>
-      </c>
-      <c r="I5" s="4">
-        <v>5300</v>
-      </c>
-      <c r="J5" s="4">
-        <v>114</v>
-      </c>
-      <c r="K5" s="4">
-        <v>393</v>
-      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
@@ -641,18 +623,10 @@
       <c r="G6" s="4">
         <v>2</v>
       </c>
-      <c r="H6" s="4">
-        <v>3</v>
-      </c>
-      <c r="I6" s="4">
-        <v>5300</v>
-      </c>
-      <c r="J6" s="4">
-        <v>98</v>
-      </c>
-      <c r="K6" s="4">
-        <v>381</v>
-      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
@@ -673,18 +647,10 @@
       <c r="G7" s="4">
         <v>3</v>
       </c>
-      <c r="H7" s="4">
-        <v>4</v>
-      </c>
-      <c r="I7" s="4">
-        <v>5300</v>
-      </c>
-      <c r="J7" s="4">
-        <v>88</v>
-      </c>
-      <c r="K7" s="4">
-        <v>367</v>
-      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
@@ -705,18 +671,10 @@
       <c r="G8" s="4">
         <v>4</v>
       </c>
-      <c r="H8" s="4">
-        <v>4</v>
-      </c>
-      <c r="I8" s="4">
-        <v>5300</v>
-      </c>
-      <c r="J8" s="4">
-        <v>78</v>
-      </c>
-      <c r="K8" s="4">
-        <v>357</v>
-      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
@@ -737,18 +695,10 @@
       <c r="G9" s="4">
         <v>5</v>
       </c>
-      <c r="H9" s="4">
-        <v>5</v>
-      </c>
-      <c r="I9" s="4">
-        <v>5300</v>
-      </c>
-      <c r="J9" s="4">
-        <v>68</v>
-      </c>
-      <c r="K9" s="4">
-        <v>343</v>
-      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
@@ -769,18 +719,10 @@
       <c r="G10" s="4">
         <v>6</v>
       </c>
-      <c r="H10" s="4">
-        <v>13</v>
-      </c>
-      <c r="I10" s="4">
-        <v>5300</v>
-      </c>
-      <c r="J10" s="4">
-        <v>52</v>
-      </c>
-      <c r="K10" s="4">
-        <v>331</v>
-      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
@@ -801,18 +743,10 @@
       <c r="G11" s="4">
         <v>7</v>
       </c>
-      <c r="H11" s="4">
-        <v>13</v>
-      </c>
-      <c r="I11" s="4">
-        <v>5300</v>
-      </c>
-      <c r="J11" s="4">
-        <v>42</v>
-      </c>
-      <c r="K11" s="4">
-        <v>321</v>
-      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
@@ -833,18 +767,10 @@
       <c r="G12" s="4">
         <v>8</v>
       </c>
-      <c r="H12" s="4">
-        <v>22</v>
-      </c>
-      <c r="I12" s="4">
-        <v>5300</v>
-      </c>
-      <c r="J12" s="4">
-        <v>32</v>
-      </c>
-      <c r="K12" s="4">
-        <v>307</v>
-      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
@@ -865,18 +791,10 @@
       <c r="G13" s="4">
         <v>9</v>
       </c>
-      <c r="H13" s="4">
-        <v>30</v>
-      </c>
-      <c r="I13" s="4">
-        <v>5300</v>
-      </c>
-      <c r="J13" s="4">
-        <v>16</v>
-      </c>
-      <c r="K13" s="4">
-        <v>295</v>
-      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
@@ -897,18 +815,10 @@
       <c r="G14" s="4">
         <v>10</v>
       </c>
-      <c r="H14" s="4">
-        <v>39</v>
-      </c>
-      <c r="I14" s="4">
-        <v>5200</v>
-      </c>
-      <c r="J14" s="4">
-        <v>10</v>
-      </c>
-      <c r="K14" s="4">
-        <v>283</v>
-      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
@@ -929,18 +839,10 @@
       <c r="G15" s="4">
         <v>11</v>
       </c>
-      <c r="H15" s="4">
-        <v>39</v>
-      </c>
-      <c r="I15" s="4">
-        <v>3460</v>
-      </c>
-      <c r="J15" s="4">
-        <v>174</v>
-      </c>
-      <c r="K15" s="4">
-        <v>273</v>
-      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
@@ -961,18 +863,10 @@
       <c r="G16" s="4">
         <v>12</v>
       </c>
-      <c r="H16" s="4">
-        <v>46</v>
-      </c>
-      <c r="I16" s="4">
-        <v>3460</v>
-      </c>
-      <c r="J16" s="4">
-        <v>158</v>
-      </c>
-      <c r="K16" s="4">
-        <v>261</v>
-      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
@@ -993,18 +887,10 @@
       <c r="G17" s="4">
         <v>13</v>
       </c>
-      <c r="H17" s="4">
-        <v>55</v>
-      </c>
-      <c r="I17" s="4">
-        <v>3460</v>
-      </c>
-      <c r="J17" s="4">
-        <v>148</v>
-      </c>
-      <c r="K17" s="4">
-        <v>247</v>
-      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
@@ -1025,18 +911,10 @@
       <c r="G18" s="4">
         <v>14</v>
       </c>
-      <c r="H18" s="4">
-        <v>55</v>
-      </c>
-      <c r="I18" s="4">
-        <v>4460</v>
-      </c>
-      <c r="J18" s="4">
-        <v>124</v>
-      </c>
-      <c r="K18" s="4">
-        <v>229</v>
-      </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
@@ -1057,18 +935,10 @@
       <c r="G19" s="4">
         <v>15</v>
       </c>
-      <c r="H19" s="4">
-        <v>55</v>
-      </c>
-      <c r="I19" s="4">
-        <v>5460</v>
-      </c>
-      <c r="J19" s="4">
-        <v>100</v>
-      </c>
-      <c r="K19" s="4">
-        <v>211</v>
-      </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
@@ -1089,18 +959,10 @@
       <c r="G20" s="4">
         <v>16</v>
       </c>
-      <c r="H20" s="4">
-        <v>55</v>
-      </c>
-      <c r="I20" s="4">
-        <v>6460</v>
-      </c>
-      <c r="J20" s="4">
-        <v>76</v>
-      </c>
-      <c r="K20" s="4">
-        <v>193</v>
-      </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
@@ -1121,18 +983,10 @@
       <c r="G21" s="4">
         <v>17</v>
       </c>
-      <c r="H21" s="4">
-        <v>55</v>
-      </c>
-      <c r="I21" s="4">
-        <v>7460</v>
-      </c>
-      <c r="J21" s="4">
-        <v>46</v>
-      </c>
-      <c r="K21" s="4">
-        <v>163</v>
-      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
@@ -1153,18 +1007,10 @@
       <c r="G22" s="4">
         <v>18</v>
       </c>
-      <c r="H22" s="4">
-        <v>55</v>
-      </c>
-      <c r="I22" s="4">
-        <v>8460</v>
-      </c>
-      <c r="J22" s="4">
-        <v>16</v>
-      </c>
-      <c r="K22" s="4">
-        <v>133</v>
-      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
@@ -1185,18 +1031,10 @@
       <c r="G23" s="4">
         <v>19</v>
       </c>
-      <c r="H23" s="4">
-        <v>62</v>
-      </c>
-      <c r="I23" s="4">
-        <v>4730</v>
-      </c>
-      <c r="J23" s="4">
-        <v>201</v>
-      </c>
-      <c r="K23" s="4">
-        <v>207</v>
-      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
@@ -1217,18 +1055,10 @@
       <c r="G24" s="4">
         <v>20</v>
       </c>
-      <c r="H24" s="4">
-        <v>55</v>
-      </c>
-      <c r="I24" s="4">
-        <v>4730</v>
-      </c>
-      <c r="J24" s="4">
-        <v>185</v>
-      </c>
-      <c r="K24" s="4">
-        <v>195</v>
-      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
@@ -1249,18 +1079,10 @@
       <c r="G25" s="4">
         <v>21</v>
       </c>
-      <c r="H25" s="4">
-        <v>55</v>
-      </c>
-      <c r="I25" s="4">
-        <v>5730</v>
-      </c>
-      <c r="J25" s="4">
-        <v>170</v>
-      </c>
-      <c r="K25" s="4">
-        <v>174</v>
-      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
@@ -1281,18 +1103,10 @@
       <c r="G26" s="4">
         <v>22</v>
       </c>
-      <c r="H26" s="4">
-        <v>55</v>
-      </c>
-      <c r="I26" s="4">
-        <v>6730</v>
-      </c>
-      <c r="J26" s="4">
-        <v>155</v>
-      </c>
-      <c r="K26" s="4">
-        <v>153</v>
-      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
@@ -1313,18 +1127,10 @@
       <c r="G27" s="4">
         <v>23</v>
       </c>
-      <c r="H27" s="4">
-        <v>55</v>
-      </c>
-      <c r="I27" s="4">
-        <v>7730</v>
-      </c>
-      <c r="J27" s="4">
-        <v>131</v>
-      </c>
-      <c r="K27" s="4">
-        <v>135</v>
-      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
@@ -1345,18 +1151,10 @@
       <c r="G28" s="4">
         <v>24</v>
       </c>
-      <c r="H28" s="4">
-        <v>55</v>
-      </c>
-      <c r="I28" s="4">
-        <v>8730</v>
-      </c>
-      <c r="J28" s="4">
-        <v>116</v>
-      </c>
-      <c r="K28" s="4">
-        <v>114</v>
-      </c>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
@@ -1369,18 +1167,10 @@
       <c r="G29" s="4">
         <v>25</v>
       </c>
-      <c r="H29" s="4">
-        <v>55</v>
-      </c>
-      <c r="I29" s="4">
-        <v>9730</v>
-      </c>
-      <c r="J29" s="4">
-        <v>86</v>
-      </c>
-      <c r="K29" s="4">
-        <v>84</v>
-      </c>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
@@ -1393,18 +1183,10 @@
       <c r="G30" s="4">
         <v>26</v>
       </c>
-      <c r="H30" s="4">
-        <v>55</v>
-      </c>
-      <c r="I30" s="4">
-        <v>10730</v>
-      </c>
-      <c r="J30" s="4">
-        <v>62</v>
-      </c>
-      <c r="K30" s="4">
-        <v>66</v>
-      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
@@ -1417,18 +1199,10 @@
       <c r="G31" s="4">
         <v>27</v>
       </c>
-      <c r="H31" s="4">
-        <v>55</v>
-      </c>
-      <c r="I31" s="4">
-        <v>11730</v>
-      </c>
-      <c r="J31" s="4">
-        <v>47</v>
-      </c>
-      <c r="K31" s="4">
-        <v>45</v>
-      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
@@ -1441,18 +1215,10 @@
       <c r="G32" s="4">
         <v>28</v>
       </c>
-      <c r="H32" s="4">
-        <v>55</v>
-      </c>
-      <c r="I32" s="4">
-        <v>12730</v>
-      </c>
-      <c r="J32" s="4">
-        <v>32</v>
-      </c>
-      <c r="K32" s="4">
-        <v>24</v>
-      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
@@ -1465,18 +1231,10 @@
       <c r="G33" s="4">
         <v>29</v>
       </c>
-      <c r="H33" s="4">
-        <v>56</v>
-      </c>
-      <c r="I33" s="4">
-        <v>12730</v>
-      </c>
-      <c r="J33" s="4">
-        <v>16</v>
-      </c>
-      <c r="K33" s="4">
-        <v>12</v>
-      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
     </row>
     <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
@@ -1489,18 +1247,10 @@
       <c r="G34" s="4">
         <v>30</v>
       </c>
-      <c r="H34" s="4">
-        <v>64</v>
-      </c>
-      <c r="I34" s="4">
-        <v>12730</v>
-      </c>
-      <c r="J34" s="4">
-        <v>0</v>
-      </c>
-      <c r="K34" s="4">
-        <v>0</v>
-      </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
